--- a/LISTAS/ma/MINI RODILLOS DISMAY.xlsx
+++ b/LISTAS/ma/MINI RODILLOS DISMAY.xlsx
@@ -712,13 +712,9 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="19" t="n">
-        <v>45168.54424231642</v>
-      </c>
-    </row>
-    <row r="2"/>
-    <row r="3"/>
-    <row r="4"/>
-    <row r="5"/>
+        <v>45219</v>
+      </c>
+    </row>
     <row r="6" ht="22.5" customHeight="1" s="1">
       <c r="A6" s="2" t="inlineStr">
         <is>
@@ -755,27 +751,6 @@
       </c>
       <c r="B10" s="6" t="n"/>
     </row>
-    <row r="11"/>
-    <row r="12"/>
-    <row r="13"/>
-    <row r="14"/>
-    <row r="15"/>
-    <row r="16"/>
-    <row r="17"/>
-    <row r="18"/>
-    <row r="19"/>
-    <row r="20"/>
-    <row r="21"/>
-    <row r="22"/>
-    <row r="23"/>
-    <row r="24"/>
-    <row r="25"/>
-    <row r="26"/>
-    <row r="27"/>
-    <row r="28"/>
-    <row r="29"/>
-    <row r="30"/>
-    <row r="31"/>
     <row r="32">
       <c r="G32" s="18" t="n"/>
     </row>
@@ -815,7 +790,7 @@
         </is>
       </c>
       <c r="D34" s="9" t="n">
-        <v>105.3</v>
+        <v>110</v>
       </c>
       <c r="E34" s="7" t="n"/>
     </row>
@@ -924,7 +899,6 @@
       </c>
       <c r="E39" s="7" t="n"/>
     </row>
-    <row r="40"/>
     <row r="41" ht="15.75" customHeight="1" s="1">
       <c r="A41" s="10" t="inlineStr">
         <is>
@@ -939,9 +913,6 @@
         </is>
       </c>
     </row>
-    <row r="43"/>
-    <row r="44"/>
-    <row r="45"/>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>

--- a/LISTAS/ma/MINI RODILLOS DISMAY.xlsx
+++ b/LISTAS/ma/MINI RODILLOS DISMAY.xlsx
@@ -712,7 +712,7 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="19" t="n">
-        <v>45219</v>
+        <v>45253</v>
       </c>
     </row>
     <row r="6" ht="22.5" customHeight="1" s="1">

--- a/LISTAS/ma/MINI RODILLOS DISMAY.xlsx
+++ b/LISTAS/ma/MINI RODILLOS DISMAY.xlsx
@@ -712,7 +712,7 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="19" t="n">
-        <v>45253</v>
+        <v>45256</v>
       </c>
     </row>
     <row r="6" ht="22.5" customHeight="1" s="1">

--- a/LISTAS/ma/MINI RODILLOS DISMAY.xlsx
+++ b/LISTAS/ma/MINI RODILLOS DISMAY.xlsx
@@ -712,7 +712,7 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="19" t="n">
-        <v>45256</v>
+        <v>45266</v>
       </c>
     </row>
     <row r="6" ht="22.5" customHeight="1" s="1">

--- a/LISTAS/ma/MINI RODILLOS DISMAY.xlsx
+++ b/LISTAS/ma/MINI RODILLOS DISMAY.xlsx
@@ -712,9 +712,13 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="19" t="n">
-        <v>45266</v>
-      </c>
-    </row>
+        <v>45258.54558960539</v>
+      </c>
+    </row>
+    <row r="2"/>
+    <row r="3"/>
+    <row r="4"/>
+    <row r="5"/>
     <row r="6" ht="22.5" customHeight="1" s="1">
       <c r="A6" s="2" t="inlineStr">
         <is>
@@ -751,6 +755,27 @@
       </c>
       <c r="B10" s="6" t="n"/>
     </row>
+    <row r="11"/>
+    <row r="12"/>
+    <row r="13"/>
+    <row r="14"/>
+    <row r="15"/>
+    <row r="16"/>
+    <row r="17"/>
+    <row r="18"/>
+    <row r="19"/>
+    <row r="20"/>
+    <row r="21"/>
+    <row r="22"/>
+    <row r="23"/>
+    <row r="24"/>
+    <row r="25"/>
+    <row r="26"/>
+    <row r="27"/>
+    <row r="28"/>
+    <row r="29"/>
+    <row r="30"/>
+    <row r="31"/>
     <row r="32">
       <c r="G32" s="18" t="n"/>
     </row>
@@ -790,7 +815,7 @@
         </is>
       </c>
       <c r="D34" s="9" t="n">
-        <v>110</v>
+        <v>180.2</v>
       </c>
       <c r="E34" s="7" t="n"/>
     </row>
@@ -811,7 +836,7 @@
         </is>
       </c>
       <c r="D35" s="9" t="n">
-        <v>117</v>
+        <v>195.5</v>
       </c>
       <c r="E35" s="7" t="n"/>
     </row>
@@ -832,7 +857,7 @@
         </is>
       </c>
       <c r="D36" s="9" t="n">
-        <v>134.6</v>
+        <v>243.4</v>
       </c>
       <c r="E36" s="7" t="n"/>
     </row>
@@ -853,7 +878,7 @@
         </is>
       </c>
       <c r="D37" s="9" t="n">
-        <v>114.7</v>
+        <v>199</v>
       </c>
       <c r="E37" s="7" t="n"/>
     </row>
@@ -874,7 +899,7 @@
         </is>
       </c>
       <c r="D38" s="9" t="n">
-        <v>128.7</v>
+        <v>216.5</v>
       </c>
       <c r="E38" s="7" t="n"/>
     </row>
@@ -895,10 +920,11 @@
         </is>
       </c>
       <c r="D39" s="9" t="n">
-        <v>160.3</v>
+        <v>244</v>
       </c>
       <c r="E39" s="7" t="n"/>
     </row>
+    <row r="40"/>
     <row r="41" ht="15.75" customHeight="1" s="1">
       <c r="A41" s="10" t="inlineStr">
         <is>
@@ -913,6 +939,9 @@
         </is>
       </c>
     </row>
+    <row r="43"/>
+    <row r="44"/>
+    <row r="45"/>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>

--- a/LISTAS/ma/MINI RODILLOS DISMAY.xlsx
+++ b/LISTAS/ma/MINI RODILLOS DISMAY.xlsx
@@ -712,13 +712,9 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="19" t="n">
-        <v>45258.54558960539</v>
-      </c>
-    </row>
-    <row r="2"/>
-    <row r="3"/>
-    <row r="4"/>
-    <row r="5"/>
+        <v>45286</v>
+      </c>
+    </row>
     <row r="6" ht="22.5" customHeight="1" s="1">
       <c r="A6" s="2" t="inlineStr">
         <is>
@@ -755,27 +751,6 @@
       </c>
       <c r="B10" s="6" t="n"/>
     </row>
-    <row r="11"/>
-    <row r="12"/>
-    <row r="13"/>
-    <row r="14"/>
-    <row r="15"/>
-    <row r="16"/>
-    <row r="17"/>
-    <row r="18"/>
-    <row r="19"/>
-    <row r="20"/>
-    <row r="21"/>
-    <row r="22"/>
-    <row r="23"/>
-    <row r="24"/>
-    <row r="25"/>
-    <row r="26"/>
-    <row r="27"/>
-    <row r="28"/>
-    <row r="29"/>
-    <row r="30"/>
-    <row r="31"/>
     <row r="32">
       <c r="G32" s="18" t="n"/>
     </row>
@@ -815,7 +790,7 @@
         </is>
       </c>
       <c r="D34" s="9" t="n">
-        <v>180.2</v>
+        <v>110</v>
       </c>
       <c r="E34" s="7" t="n"/>
     </row>
@@ -836,7 +811,7 @@
         </is>
       </c>
       <c r="D35" s="9" t="n">
-        <v>195.5</v>
+        <v>117</v>
       </c>
       <c r="E35" s="7" t="n"/>
     </row>
@@ -857,7 +832,7 @@
         </is>
       </c>
       <c r="D36" s="9" t="n">
-        <v>243.4</v>
+        <v>134.6</v>
       </c>
       <c r="E36" s="7" t="n"/>
     </row>
@@ -878,7 +853,7 @@
         </is>
       </c>
       <c r="D37" s="9" t="n">
-        <v>199</v>
+        <v>114.7</v>
       </c>
       <c r="E37" s="7" t="n"/>
     </row>
@@ -899,7 +874,7 @@
         </is>
       </c>
       <c r="D38" s="9" t="n">
-        <v>216.5</v>
+        <v>128.7</v>
       </c>
       <c r="E38" s="7" t="n"/>
     </row>
@@ -920,11 +895,10 @@
         </is>
       </c>
       <c r="D39" s="9" t="n">
-        <v>244</v>
+        <v>160.3</v>
       </c>
       <c r="E39" s="7" t="n"/>
     </row>
-    <row r="40"/>
     <row r="41" ht="15.75" customHeight="1" s="1">
       <c r="A41" s="10" t="inlineStr">
         <is>
@@ -939,9 +913,6 @@
         </is>
       </c>
     </row>
-    <row r="43"/>
-    <row r="44"/>
-    <row r="45"/>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
